--- a/data/trans_orig/P36BPD05_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023</t>
+          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161397</t>
+          <t>160054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214395</t>
+          <t>213612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144958</t>
+          <t>145754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181525</t>
+          <t>182559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>317594</t>
+          <t>317156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>379669</t>
+          <t>381170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418868</t>
+          <t>419651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471866</t>
+          <t>473209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>490866</t>
+          <t>489832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>527433</t>
+          <t>526637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925985</t>
+          <t>924484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>988060</t>
+          <t>988498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399194</t>
+          <t>398828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>875793</t>
+          <t>863733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277959</t>
+          <t>279726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>327930</t>
+          <t>326223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>697500</t>
+          <t>693690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1328502</t>
+          <t>1277234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313522</t>
+          <t>325582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>790121</t>
+          <t>790487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>629631</t>
+          <t>631338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>679602</t>
+          <t>677835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818374</t>
+          <t>869642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1449376</t>
+          <t>1453186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>192159</t>
+          <t>191860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249618</t>
+          <t>249113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210259</t>
+          <t>207981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>635631</t>
+          <t>661973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>434630</t>
+          <t>435917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>942986</t>
+          <t>922174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453787</t>
+          <t>454292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511246</t>
+          <t>511545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296670</t>
+          <t>270328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>722042</t>
+          <t>724320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>692720</t>
+          <t>713532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1201076</t>
+          <t>1199789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267859</t>
+          <t>266945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>329172</t>
+          <t>325994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292795</t>
+          <t>295454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>525922</t>
+          <t>504918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>582553</t>
+          <t>583904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>835337</t>
+          <t>806548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>599832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>657967</t>
+          <t>658881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564493</t>
+          <t>585497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>797620</t>
+          <t>794961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1180904</t>
+          <t>1209693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1433688</t>
+          <t>1432337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1084725</t>
+          <t>1085184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1769508</t>
+          <t>1775515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1001414</t>
+          <t>1012666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1635317</t>
+          <t>1655036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2149513</t>
+          <t>2172576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3110770</t>
+          <t>3117474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1682301</t>
+          <t>1676294</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2367084</t>
+          <t>2366625</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2017350</t>
+          <t>1997631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2651253</t>
+          <t>2640001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3993707</t>
+          <t>3987003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4954964</t>
+          <t>4931901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD05_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>185897</t>
+          <t>201053</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160054</t>
+          <t>176903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213612</t>
+          <t>228298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>162163</t>
+          <t>177307</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145754</t>
+          <t>159102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>182559</t>
+          <t>200466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>348060</t>
+          <t>378360</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>317156</t>
+          <t>346985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381170</t>
+          <t>410645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>447366</t>
+          <t>487290</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419651</t>
+          <t>460045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473209</t>
+          <t>511440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>510228</t>
+          <t>552261</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>489832</t>
+          <t>529102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>526637</t>
+          <t>570466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>957594</t>
+          <t>1039551</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>924484</t>
+          <t>1007266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>988498</t>
+          <t>1070926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633263</t>
+          <t>688343</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>633263</t>
+          <t>688343</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633263</t>
+          <t>688343</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>672391</t>
+          <t>729568</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>672391</t>
+          <t>729568</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>672391</t>
+          <t>729568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1305654</t>
+          <t>1417911</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1305654</t>
+          <t>1417911</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1305654</t>
+          <t>1417911</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>571817</t>
+          <t>349558</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>398828</t>
+          <t>315800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>863733</t>
+          <t>385232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>302661</t>
+          <t>346038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279726</t>
+          <t>318475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>326223</t>
+          <t>375346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>874478</t>
+          <t>695596</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>693690</t>
+          <t>653261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1277234</t>
+          <t>741224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>617498</t>
+          <t>695526</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325582</t>
+          <t>659852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>790487</t>
+          <t>729284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>654900</t>
+          <t>724256</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>631338</t>
+          <t>694948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>677835</t>
+          <t>751819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1272398</t>
+          <t>1419781</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>869642</t>
+          <t>1374153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1453186</t>
+          <t>1462116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1189315</t>
+          <t>1045084</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1189315</t>
+          <t>1045084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1189315</t>
+          <t>1045084</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957561</t>
+          <t>1070294</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957561</t>
+          <t>1070294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957561</t>
+          <t>1070294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2146876</t>
+          <t>2115377</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2146876</t>
+          <t>2115377</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2146876</t>
+          <t>2115377</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>218681</t>
+          <t>254920</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191860</t>
+          <t>224765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249113</t>
+          <t>285751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>377782</t>
+          <t>194017</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207981</t>
+          <t>172673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>661973</t>
+          <t>217576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>596463</t>
+          <t>448936</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>435917</t>
+          <t>410397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>922174</t>
+          <t>487706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>484724</t>
+          <t>546867</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454292</t>
+          <t>516036</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511545</t>
+          <t>577022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>554519</t>
+          <t>617068</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>270328</t>
+          <t>593509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>724320</t>
+          <t>638412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1039243</t>
+          <t>1163936</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>713532</t>
+          <t>1125166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1199789</t>
+          <t>1202475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>801787</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>801787</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703405</t>
+          <t>801787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932301</t>
+          <t>811085</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932301</t>
+          <t>811085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932301</t>
+          <t>811085</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635706</t>
+          <t>1612872</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635706</t>
+          <t>1612872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635706</t>
+          <t>1612872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>294785</t>
+          <t>330416</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266945</t>
+          <t>301043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325994</t>
+          <t>362529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>352075</t>
+          <t>320142</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295454</t>
+          <t>293357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>504918</t>
+          <t>349098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>646860</t>
+          <t>650558</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>583904</t>
+          <t>610784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>806548</t>
+          <t>697563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>631041</t>
+          <t>658712</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599832</t>
+          <t>626599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>658881</t>
+          <t>688085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>738340</t>
+          <t>793735</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>585497</t>
+          <t>764779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>794961</t>
+          <t>820520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1369381</t>
+          <t>1452447</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1209693</t>
+          <t>1405442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432337</t>
+          <t>1492221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090415</t>
+          <t>1113877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090415</t>
+          <t>1113877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090415</t>
+          <t>1113877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016241</t>
+          <t>2103005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016241</t>
+          <t>2103005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016241</t>
+          <t>2103005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1271181</t>
+          <t>1135946</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1085184</t>
+          <t>1071950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1775515</t>
+          <t>1202254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1194680</t>
+          <t>1037504</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1012666</t>
+          <t>989836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1655036</t>
+          <t>1087056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2465861</t>
+          <t>2173450</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2172576</t>
+          <t>2091863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3117474</t>
+          <t>2250672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2180628</t>
+          <t>2388395</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1676294</t>
+          <t>2322087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2366625</t>
+          <t>2452391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2457987</t>
+          <t>2687320</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1997631</t>
+          <t>2637768</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2640001</t>
+          <t>2734988</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4638616</t>
+          <t>5075715</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3987003</t>
+          <t>4998493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4931901</t>
+          <t>5157302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3451809</t>
+          <t>3524341</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3652667</t>
+          <t>3724824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7104477</t>
+          <t>7249165</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
